--- a/JsonConverter/ExcelFiles/Achievement.xlsx
+++ b/JsonConverter/ExcelFiles/Achievement.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
   <si>
     <t>아이디</t>
   </si>
@@ -38,6 +38,9 @@
     <t>업적 종류</t>
   </si>
   <si>
+    <t>어떤 이벤트에 반응하는지 체크</t>
+  </si>
+  <si>
     <t>업적 점수</t>
   </si>
   <si>
@@ -62,6 +65,9 @@
     <t>AchievementType</t>
   </si>
   <si>
+    <t>TriggerType</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -101,6 +107,9 @@
     <t>Stacked</t>
   </si>
   <si>
+    <t>FoodDelivered</t>
+  </si>
+  <si>
     <t>Achievement_102</t>
   </si>
   <si>
@@ -137,6 +146,9 @@
     <t>제련이 뭔지는 알아</t>
   </si>
   <si>
+    <t>IngotRefined</t>
+  </si>
+  <si>
     <t>Achievement_112</t>
   </si>
   <si>
@@ -174,6 +186,9 @@
   </si>
   <si>
     <t>Acomplished</t>
+  </si>
+  <si>
+    <t>StageClear</t>
   </si>
   <si>
     <t>Stage_normal_00</t>
@@ -1363,25 +1378,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16.2222222222222" customWidth="1"/>
     <col min="2" max="2" width="28.7777777777778" customWidth="1"/>
-    <col min="3" max="3" width="18.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="13.6666666666667" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="17.5555555555556" customWidth="1"/>
-    <col min="7" max="7" width="18.5555555555556" customWidth="1"/>
-    <col min="8" max="8" width="31.8888888888889" customWidth="1"/>
-    <col min="9" max="9" width="16.2222222222222" customWidth="1"/>
-    <col min="10" max="10" width="11.8888888888889" customWidth="1"/>
-    <col min="11" max="11" width="106.777777777778" customWidth="1"/>
-    <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="15.5555555555556" customWidth="1"/>
+    <col min="3" max="4" width="18.6666666666667" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.1111111111111" customWidth="1"/>
+    <col min="7" max="7" width="17.5555555555556" customWidth="1"/>
+    <col min="8" max="8" width="18.5555555555556" customWidth="1"/>
+    <col min="9" max="9" width="31.8888888888889" customWidth="1"/>
+    <col min="10" max="10" width="16.2222222222222" customWidth="1"/>
+    <col min="11" max="11" width="11.8888888888889" customWidth="1"/>
+    <col min="12" max="12" width="106.777777777778" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="15.5555555555556" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1409,306 +1424,342 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" t="s">
-        <v>9</v>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s">
-        <v>20</v>
-      </c>
+      <c r="F4">
+        <v>100</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="1"/>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4">
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5">
+        <v>50</v>
+      </c>
+      <c r="F5">
+        <v>500</v>
+      </c>
+      <c r="H5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6">
+        <v>200</v>
+      </c>
+      <c r="F6">
+        <v>1000</v>
+      </c>
+      <c r="I6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7">
         <v>10</v>
       </c>
-      <c r="E4">
+      <c r="F7">
         <v>100</v>
       </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="H7" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" t="s">
+        <v>42</v>
+      </c>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
         <v>25</v>
       </c>
-      <c r="I4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" s="1"/>
+      <c r="D8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>500</v>
+      </c>
+      <c r="H8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" s="1"/>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5">
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9">
+        <v>200</v>
+      </c>
+      <c r="F9">
+        <v>1000</v>
+      </c>
+      <c r="I9" t="s">
+        <v>48</v>
+      </c>
+      <c r="J9" t="s">
+        <v>49</v>
+      </c>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
         <v>50</v>
       </c>
-      <c r="E5">
-        <v>500</v>
-      </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="1"/>
+      <c r="B10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" t="s">
+        <v>57</v>
+      </c>
+      <c r="K10" s="1"/>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6">
-        <v>200</v>
-      </c>
-      <c r="E6">
-        <v>1000</v>
-      </c>
-      <c r="H6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J6" s="1"/>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11">
+        <v>100</v>
+      </c>
+      <c r="G11" t="s">
+        <v>59</v>
+      </c>
+      <c r="H11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" s="1"/>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7">
-        <v>10</v>
-      </c>
-      <c r="E7">
-        <v>100</v>
-      </c>
-      <c r="G7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="1"/>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12">
+        <v>300</v>
+      </c>
+      <c r="G12" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" t="s">
+        <v>65</v>
+      </c>
+      <c r="J12" t="s">
+        <v>66</v>
+      </c>
+      <c r="K12" s="1"/>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8">
-        <v>50</v>
-      </c>
-      <c r="E8">
-        <v>500</v>
-      </c>
-      <c r="G8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="1"/>
+    <row r="13" spans="1:11">
+      <c r="B13" s="2"/>
+      <c r="K13" s="1"/>
     </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9">
-        <v>200</v>
-      </c>
-      <c r="E9">
-        <v>1000</v>
-      </c>
-      <c r="H9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" t="s">
-        <v>45</v>
-      </c>
-      <c r="J9" s="1"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" t="s">
-        <v>50</v>
-      </c>
-      <c r="H10" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10" s="1"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11">
-        <v>100</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="1"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12">
-        <v>300</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="H12" t="s">
-        <v>60</v>
-      </c>
-      <c r="I12" t="s">
-        <v>61</v>
-      </c>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="B13" s="2"/>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:11">
       <c r="B14" s="2"/>
-      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/Achievement.xlsx
+++ b/JsonConverter/ExcelFiles/Achievement.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="16524" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -185,7 +185,7 @@
     <t>초보 운전</t>
   </si>
   <si>
-    <t>Acomplished</t>
+    <t>Accomplished</t>
   </si>
   <si>
     <t>StageClear</t>

--- a/JsonConverter/ExcelFiles/Achievement.xlsx
+++ b/JsonConverter/ExcelFiles/Achievement.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="98">
   <si>
     <t>아이디</t>
   </si>
@@ -116,7 +116,7 @@
     <t>행성에 식량을 총 100개 배달한다.</t>
   </si>
   <si>
-    <t>Achievement_0</t>
+    <t>AchievementInfo1_0</t>
   </si>
   <si>
     <t>이 정도면 나도 배달 좀 하는데?</t>
@@ -128,7 +128,7 @@
     <t>행성에 식량을 총 500개 배달한다.</t>
   </si>
   <si>
-    <t>Achievement_1</t>
+    <t>AchievementInfo1_1</t>
   </si>
   <si>
     <t>밥은 내가 책임진다</t>
@@ -137,7 +137,7 @@
     <t>행성에 식량을 총 1000개 배달한다.</t>
   </si>
   <si>
-    <t>Achievement_2</t>
+    <t>AchievementInfo1_2</t>
   </si>
   <si>
     <t>Achievement_111</t>
@@ -155,7 +155,7 @@
     <t>주괴를 총 100개 제련한다.</t>
   </si>
   <si>
-    <t>Achievement_3</t>
+    <t>AchievementInfo1_3</t>
   </si>
   <si>
     <t>이제 대장장이가 뭔지 깨달았어</t>
@@ -167,7 +167,7 @@
     <t>주괴를 총 500개 제련한다.</t>
   </si>
   <si>
-    <t>Achievement_4</t>
+    <t>AchievementInfo1_4</t>
   </si>
   <si>
     <t>우리 동네 대장장이</t>
@@ -176,7 +176,7 @@
     <t>주괴를 총 1000개 제련한다.</t>
   </si>
   <si>
-    <t>Achievement_5</t>
+    <t>AchievementInfo1_5</t>
   </si>
   <si>
     <t>Achievement_201</t>
@@ -200,7 +200,7 @@
     <t>튜토리얼 스테이지를 클리어한다</t>
   </si>
   <si>
-    <t>Achievement_6</t>
+    <t>AchievementInfo1_6</t>
   </si>
   <si>
     <t>나도 이제 어엿한 배달부</t>
@@ -215,7 +215,7 @@
     <t>노말 스테이지 5를 클리어한다.</t>
   </si>
   <si>
-    <t>Achievement_7</t>
+    <t>AchievementInfo1_7</t>
   </si>
   <si>
     <t>스피드 레이서</t>
@@ -227,7 +227,100 @@
     <t>노말 스테이지를 모두 클리어한다.</t>
   </si>
   <si>
-    <t>Achievement_8</t>
+    <t>AchievementInfo1_8</t>
+  </si>
+  <si>
+    <t>Achievement_301</t>
+  </si>
+  <si>
+    <t>좀 빠른 편</t>
+  </si>
+  <si>
+    <t>SpeedReached</t>
+  </si>
+  <si>
+    <t>Achievement_302</t>
+  </si>
+  <si>
+    <t>우주선 속도를 10에 도달한다.</t>
+  </si>
+  <si>
+    <t>AchievementInfo2_0</t>
+  </si>
+  <si>
+    <t>이 정도면 쾌속</t>
+  </si>
+  <si>
+    <t>Achievement_303</t>
+  </si>
+  <si>
+    <t>우주선 속도를 20에 도달한다.</t>
+  </si>
+  <si>
+    <t>AchievementInfo2_1</t>
+  </si>
+  <si>
+    <t>빛보다 빠를 순 없지</t>
+  </si>
+  <si>
+    <t>우주선 속도를 30에 도달한다.</t>
+  </si>
+  <si>
+    <t>AchievementInfo2_2</t>
+  </si>
+  <si>
+    <t>Achievement_311</t>
+  </si>
+  <si>
+    <t>업그레이드 입문</t>
+  </si>
+  <si>
+    <t>UpgradeCompleted</t>
+  </si>
+  <si>
+    <t>Achievement_312</t>
+  </si>
+  <si>
+    <t>우주선 업그레이드를 총 5회 완료한다.</t>
+  </si>
+  <si>
+    <t>AchievementInfo2_3</t>
+  </si>
+  <si>
+    <t>업그레이드 중독자</t>
+  </si>
+  <si>
+    <t>Achievement_313</t>
+  </si>
+  <si>
+    <t>우주선 업그레이드를 총 10회 완료한다.</t>
+  </si>
+  <si>
+    <t>AchievementInfo2_4</t>
+  </si>
+  <si>
+    <t>풀업 그게 뭔데</t>
+  </si>
+  <si>
+    <t>우주선 업그레이드를 총 15회 완료한다.</t>
+  </si>
+  <si>
+    <t>AchievementInfo2_5</t>
+  </si>
+  <si>
+    <t>Achievement_401</t>
+  </si>
+  <si>
+    <t>비밀을 아는 자</t>
+  </si>
+  <si>
+    <t>HiddenCodeFound</t>
+  </si>
+  <si>
+    <t>숨겨진 코드를 발견한다.</t>
+  </si>
+  <si>
+    <t>AchievementInfo2_6</t>
   </si>
 </sst>
 </file>
@@ -1378,7 +1471,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="16.2222222222222" customWidth="1"/>
@@ -1389,7 +1482,7 @@
     <col min="7" max="7" width="17.5555555555556" customWidth="1"/>
     <col min="8" max="8" width="18.5555555555556" customWidth="1"/>
     <col min="9" max="9" width="31.8888888888889" customWidth="1"/>
-    <col min="10" max="10" width="16.2222222222222" customWidth="1"/>
+    <col min="10" max="10" width="21.7777777777778" customWidth="1"/>
     <col min="11" max="11" width="11.8888888888889" customWidth="1"/>
     <col min="12" max="12" width="106.777777777778" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
@@ -1754,12 +1847,197 @@
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11">
-      <c r="B13" s="2"/>
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" t="s">
+        <v>72</v>
+      </c>
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11">
-      <c r="B14" s="2"/>
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14">
+        <v>50</v>
+      </c>
+      <c r="F14">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14" t="s">
+        <v>75</v>
+      </c>
+      <c r="J14" t="s">
+        <v>76</v>
+      </c>
       <c r="K14" s="1"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15">
+        <v>200</v>
+      </c>
+      <c r="F15">
+        <v>30</v>
+      </c>
+      <c r="I15" t="s">
+        <v>78</v>
+      </c>
+      <c r="J15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" t="s">
+        <v>81</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>5</v>
+      </c>
+      <c r="H16" t="s">
+        <v>83</v>
+      </c>
+      <c r="I16" t="s">
+        <v>84</v>
+      </c>
+      <c r="J16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B17" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17">
+        <v>50</v>
+      </c>
+      <c r="F17">
+        <v>10</v>
+      </c>
+      <c r="H17" t="s">
+        <v>87</v>
+      </c>
+      <c r="I17" t="s">
+        <v>88</v>
+      </c>
+      <c r="J17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18">
+        <v>200</v>
+      </c>
+      <c r="F18">
+        <v>15</v>
+      </c>
+      <c r="I18" t="s">
+        <v>91</v>
+      </c>
+      <c r="J18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19">
+        <v>500</v>
+      </c>
+      <c r="I19" t="s">
+        <v>96</v>
+      </c>
+      <c r="J19" t="s">
+        <v>97</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/JsonConverter/ExcelFiles/Achievement.xlsx
+++ b/JsonConverter/ExcelFiles/Achievement.xlsx
@@ -242,7 +242,7 @@
     <t>Achievement_302</t>
   </si>
   <si>
-    <t>우주선 속도를 10에 도달한다.</t>
+    <t>우주선 속도가 15에 도달한다.</t>
   </si>
   <si>
     <t>AchievementInfo2_0</t>
@@ -254,7 +254,7 @@
     <t>Achievement_303</t>
   </si>
   <si>
-    <t>우주선 속도를 20에 도달한다.</t>
+    <t>우주선 속도를 30에 도달한다.</t>
   </si>
   <si>
     <t>AchievementInfo2_1</t>
@@ -263,7 +263,7 @@
     <t>빛보다 빠를 순 없지</t>
   </si>
   <si>
-    <t>우주선 속도를 30에 도달한다.</t>
+    <t>우주선 속도를 45에 도달한다.</t>
   </si>
   <si>
     <t>AchievementInfo2_2</t>
@@ -1863,7 +1863,7 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H13" t="s">
         <v>70</v>
@@ -1893,7 +1893,7 @@
         <v>50</v>
       </c>
       <c r="F14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H14" t="s">
         <v>74</v>
@@ -1923,7 +1923,7 @@
         <v>200</v>
       </c>
       <c r="F15">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="I15" t="s">
         <v>78</v>
